--- a/artfynd/A 60864-2023 artfynd.xlsx
+++ b/artfynd/A 60864-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119744285</v>
+        <v>119742606</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>90527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587510</v>
+        <v>587511</v>
       </c>
       <c r="R2" t="n">
-        <v>6963377</v>
+        <v>6963384</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119742606</v>
+        <v>119744285</v>
       </c>
       <c r="B3" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587511</v>
+        <v>587510</v>
       </c>
       <c r="R3" t="n">
-        <v>6963384</v>
+        <v>6963377</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 60864-2023 artfynd.xlsx
+++ b/artfynd/A 60864-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119742606</v>
+        <v>119744285</v>
       </c>
       <c r="B2" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587511</v>
+        <v>587510</v>
       </c>
       <c r="R2" t="n">
-        <v>6963384</v>
+        <v>6963377</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119744285</v>
+        <v>119742606</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>90527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587510</v>
+        <v>587511</v>
       </c>
       <c r="R3" t="n">
-        <v>6963377</v>
+        <v>6963384</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 60864-2023 artfynd.xlsx
+++ b/artfynd/A 60864-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119742606</v>
       </c>
       <c r="B2" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>119744285</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>119830584</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 60864-2023 artfynd.xlsx
+++ b/artfynd/A 60864-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,6 +987,120 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119830541</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hattberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>587458</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6963452</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Norberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Norberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60864-2023 artfynd.xlsx
+++ b/artfynd/A 60864-2023 artfynd.xlsx
@@ -992,7 +992,7 @@
         <v>119830541</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60864-2023 artfynd.xlsx
+++ b/artfynd/A 60864-2023 artfynd.xlsx
@@ -992,7 +992,7 @@
         <v>119830541</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60864-2023 artfynd.xlsx
+++ b/artfynd/A 60864-2023 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>119830584</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>119830541</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60864-2023 artfynd.xlsx
+++ b/artfynd/A 60864-2023 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>119830584</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>119830541</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60864-2023 artfynd.xlsx
+++ b/artfynd/A 60864-2023 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>119830584</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>119830541</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60864-2023 artfynd.xlsx
+++ b/artfynd/A 60864-2023 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>119830584</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>119830541</v>
       </c>
       <c r="B5" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60864-2023 artfynd.xlsx
+++ b/artfynd/A 60864-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119742606</v>
+        <v>119742721</v>
       </c>
       <c r="B2" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587511</v>
+        <v>587507</v>
       </c>
       <c r="R2" t="n">
-        <v>6963384</v>
+        <v>6963360</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119744285</v>
+        <v>119742699</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587510</v>
+        <v>587501</v>
       </c>
       <c r="R3" t="n">
-        <v>6963377</v>
+        <v>6963353</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119830584</v>
+        <v>119744285</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,45 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hattberget, Mpd</t>
+          <t>Rödmyran, Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587455</v>
+        <v>587510</v>
       </c>
       <c r="R4" t="n">
-        <v>6963467</v>
+        <v>6963377</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,77 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119830541</v>
+        <v>119742606</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hattberget, Mpd</t>
+          <t>Rödmyran, Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587458</v>
+        <v>587511</v>
       </c>
       <c r="R5" t="n">
-        <v>6963452</v>
+        <v>6963384</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,15 +1051,326 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119830541</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hattberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>587458</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6963452</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Andreas Norberg</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Andreas Norberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119830584</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hattberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>587455</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6963467</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andreas Norberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Norberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119746642</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hattberget, Hattberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>587513</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6963470</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60864-2023 artfynd.xlsx
+++ b/artfynd/A 60864-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119742721</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119742699</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119744285</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119742606</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830541</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830584</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,8 +1406,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119746642</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>